--- a/output/yearly_surface_area_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_85_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497648944556</v>
+        <v>10.84497637757489</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907248977557</v>
+        <v>37.78907209996481</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.237624002156734</v>
+        <v>6.496224559001145</v>
       </c>
       <c r="C2" t="n">
-        <v>5.165956419746716</v>
+        <v>14.10378751920968</v>
       </c>
       <c r="D2" t="n">
-        <v>21.31865139771949</v>
+        <v>28.98119222936584</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.17567608579795</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C3" t="n">
-        <v>35.90251354430585</v>
+        <v>33.7328511179204</v>
       </c>
       <c r="D3" t="n">
-        <v>48.82722207071512</v>
+        <v>80.36095833112267</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.40003864618074</v>
+        <v>35.68456555396306</v>
       </c>
       <c r="C4" t="n">
-        <v>83.4299016545982</v>
+        <v>81.93666339643879</v>
       </c>
       <c r="D4" t="n">
-        <v>56.61542660850506</v>
+        <v>84.14461398328987</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.31332605303754</v>
+        <v>40.81616080406115</v>
       </c>
       <c r="C5" t="n">
-        <v>125.9582304548658</v>
+        <v>123.3075116533994</v>
       </c>
       <c r="D5" t="n">
-        <v>47.00117134081605</v>
+        <v>55.07604620824608</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>37.35353665118265</v>
       </c>
       <c r="C6" t="n">
-        <v>159.1550473262675</v>
+        <v>126.3499477888603</v>
       </c>
       <c r="D6" t="n">
-        <v>39.68813269188156</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.14670668075605</v>
+        <v>27.90716024091983</v>
       </c>
       <c r="C7" t="n">
-        <v>157.2023511425205</v>
+        <v>123.9652826152447</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>106.730701667192</v>
+        <v>84.78373173875454</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>46.59374604355361</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.669008450669652</v>
+        <v>7.683216267696436</v>
       </c>
       <c r="C21" t="n">
-        <v>92.98672746436952</v>
+        <v>94.11939927928132</v>
       </c>
       <c r="D21" t="n">
-        <v>7.669008450669652</v>
+        <v>8.64361830115849</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.752460709809561</v>
+        <v>5.755005042294803</v>
       </c>
       <c r="C2" t="n">
-        <v>18.94674894425919</v>
+        <v>11.20272305316035</v>
       </c>
       <c r="D2" t="n">
-        <v>18.55012287174348</v>
+        <v>26.39526877637974</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36711688812607</v>
+        <v>19.29625112697106</v>
       </c>
       <c r="C3" t="n">
-        <v>27.70001147532376</v>
+        <v>44.15901173702153</v>
       </c>
       <c r="D3" t="n">
-        <v>53.40216637250525</v>
+        <v>83.7381704337317</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.57046183609218</v>
+        <v>34.15303913533804</v>
       </c>
       <c r="C4" t="n">
-        <v>86.35256457014096</v>
+        <v>82.94491828870026</v>
       </c>
       <c r="D4" t="n">
-        <v>66.36614480708438</v>
+        <v>101.9486085998058</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.57763716965817</v>
+        <v>46.16668579220627</v>
       </c>
       <c r="C5" t="n">
-        <v>137.665571828009</v>
+        <v>135.0148530265426</v>
       </c>
       <c r="D5" t="n">
-        <v>54.60971604872884</v>
+        <v>69.26230053461248</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.69821221083129</v>
+        <v>45.24286120251001</v>
       </c>
       <c r="C6" t="n">
-        <v>178.5563454575929</v>
+        <v>158.6317757999039</v>
       </c>
       <c r="D6" t="n">
-        <v>44.88059629964295</v>
+        <v>47.37619896383834</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.24947139453248</v>
+        <v>35.45287309576081</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9004401801648</v>
+        <v>150.2555043872701</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>40.24380189248525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.69662426385451</v>
+        <v>22.03041848329842</v>
       </c>
       <c r="C8" t="n">
-        <v>153.962583718506</v>
+        <v>120.9169559935584</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>87.97343002985241</v>
+        <v>73.77343123562655</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>33.05151821117311</v>
@@ -1237,7 +1237,7 @@
         <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.84374528783103</v>
+        <v>7.859072271496631</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9882205808245</v>
+        <v>102.1679395294562</v>
       </c>
       <c r="D21" t="n">
-        <v>8.824213448809909</v>
+        <v>9.823840339370788</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.967463457039614</v>
+        <v>6.775040907007239</v>
       </c>
       <c r="C2" t="n">
-        <v>13.90940147376881</v>
+        <v>13.19272564966864</v>
       </c>
       <c r="D2" t="n">
-        <v>24.1313585703866</v>
+        <v>33.13202152292136</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.31097734253476</v>
+        <v>18.87409961414493</v>
       </c>
       <c r="C3" t="n">
-        <v>48.23326470964579</v>
+        <v>43.45215338996383</v>
       </c>
       <c r="D3" t="n">
-        <v>54.70298208063227</v>
+        <v>84.16523068507905</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.26415655236718</v>
+        <v>34.43381897875263</v>
       </c>
       <c r="C4" t="n">
-        <v>77.66115214444393</v>
+        <v>93.88256946171398</v>
       </c>
       <c r="D4" t="n">
-        <v>74.13864138160638</v>
+        <v>114.5326506728414</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.4612101034803</v>
+        <v>48.27744335633691</v>
       </c>
       <c r="C5" t="n">
-        <v>146.5013011662303</v>
+        <v>141.0035140224482</v>
       </c>
       <c r="D5" t="n">
-        <v>63.44544538695013</v>
+        <v>85.41205026947252</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.01143078621504</v>
+        <v>51.76362945411734</v>
       </c>
       <c r="C6" t="n">
-        <v>193.8519746897582</v>
+        <v>182.5412593891307</v>
       </c>
       <c r="D6" t="n">
-        <v>49.83154997215961</v>
+        <v>55.18502020341747</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.03473068920969</v>
+        <v>42.75903951076558</v>
       </c>
       <c r="C7" t="n">
-        <v>217.6279405912074</v>
+        <v>182.2948407153647</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.12354564648163</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="C8" t="n">
-        <v>196.1875524781613</v>
+        <v>153.4618923893402</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>129.3531140161512</v>
+        <v>106.0562409943744</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>69.18376071827274</v>
+        <v>60.21549543997811</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>41.40324593120072</v>
+        <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
         <v>36.96083756948391</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.001659108401107</v>
+        <v>8.01805388975732</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0223979634149</v>
+        <v>109.2459842479435</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00207388550138</v>
+        <v>11.02482409841632</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.46971737098648</v>
+        <v>6.295948027334795</v>
       </c>
       <c r="C2" t="n">
-        <v>9.680032363873551</v>
+        <v>9.18130453011617</v>
       </c>
       <c r="D2" t="n">
-        <v>19.82934013037708</v>
+        <v>27.31320287985051</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.58019719767664</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="C3" t="n">
-        <v>66.15016031215008</v>
+        <v>63.82341825308514</v>
       </c>
       <c r="D3" t="n">
-        <v>58.64469911318322</v>
+        <v>90.28642762105792</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.32199755145973</v>
+        <v>23.18986252201391</v>
       </c>
       <c r="C4" t="n">
-        <v>114.877244117032</v>
+        <v>120.8501971496696</v>
       </c>
       <c r="D4" t="n">
-        <v>71.1904530257532</v>
+        <v>105.4583566424881</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.84513020910304</v>
+        <v>29.15790681613028</v>
       </c>
       <c r="C5" t="n">
-        <v>115.8216854085175</v>
+        <v>109.0721699418207</v>
       </c>
       <c r="D5" t="n">
-        <v>46.82936549257286</v>
+        <v>55.93507544946203</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.93464917663875</v>
+        <v>26.52584122104457</v>
       </c>
       <c r="C6" t="n">
-        <v>143.3361465677386</v>
+        <v>120.0706894724977</v>
       </c>
       <c r="D6" t="n">
-        <v>28.29691407950582</v>
+        <v>28.94094057349173</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>137.9188627357046</v>
+        <v>107.9156711462179</v>
       </c>
       <c r="D7" t="n">
-        <v>27.48795397120644</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>95.29824965123788</v>
+        <v>78.10784734987622</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>45.92812110007426</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
         <v>28.89774367450487</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.47216389248049</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.994731408580272</v>
+        <v>3.878885179479147</v>
       </c>
       <c r="C2" t="n">
-        <v>4.855724145204724</v>
+        <v>4.461061568097507</v>
       </c>
       <c r="D2" t="n">
-        <v>13.68163600638355</v>
+        <v>19.8362123643068</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.9778050178966</v>
+        <v>22.96307880233289</v>
       </c>
       <c r="C3" t="n">
-        <v>53.01437602932776</v>
+        <v>50.83489612589984</v>
       </c>
       <c r="D3" t="n">
-        <v>61.33468782281948</v>
+        <v>92.24501429103032</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.9495963763807</v>
+        <v>31.84298678724529</v>
       </c>
       <c r="C4" t="n">
-        <v>141.5640919615731</v>
+        <v>142.1511770887127</v>
       </c>
       <c r="D4" t="n">
-        <v>81.41339187007524</v>
+        <v>121.8712147620863</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.03581024790518</v>
+        <v>32.81491701444964</v>
       </c>
       <c r="C5" t="n">
-        <v>161.3256915003572</v>
+        <v>161.742934274662</v>
       </c>
       <c r="D5" t="n">
-        <v>57.97220193577417</v>
+        <v>74.17103905584653</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C6" t="n">
-        <v>167.768901683329</v>
+        <v>147.1600538757799</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96610616090365</v>
+        <v>34.85793398698726</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>167.8621677152324</v>
+        <v>134.3256661381613</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>29.94330497952771</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>124.7555895171634</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>57.243745139223</v>
+        <v>49.81093327037041</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>29.75186417719959</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.031056073637403</v>
+        <v>3.567671157232909</v>
       </c>
       <c r="C2" t="n">
-        <v>11.16639838810322</v>
+        <v>6.752460709809561</v>
       </c>
       <c r="D2" t="n">
-        <v>14.24515918862122</v>
+        <v>18.48238228015045</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.29486846863931</v>
+        <v>18.09851892778995</v>
       </c>
       <c r="C3" t="n">
-        <v>35.15638528907828</v>
+        <v>33.32051708213675</v>
       </c>
       <c r="D3" t="n">
-        <v>58.17346021514475</v>
+        <v>86.98775533478863</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.70558316637975</v>
+        <v>37.43305821522663</v>
       </c>
       <c r="C4" t="n">
-        <v>136.8291227839907</v>
+        <v>135.7570542909532</v>
       </c>
       <c r="D4" t="n">
-        <v>91.6746188748629</v>
+        <v>137.4162079111303</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.09810232162923</v>
+        <v>38.99992755120455</v>
       </c>
       <c r="C5" t="n">
-        <v>210.609426253547</v>
+        <v>208.7195619228719</v>
       </c>
       <c r="D5" t="n">
-        <v>71.34851440613696</v>
+        <v>96.50579932746149</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>37.27303333943441</v>
       </c>
       <c r="C6" t="n">
-        <v>207.9803059015741</v>
+        <v>196.7903455685689</v>
       </c>
       <c r="D6" t="n">
-        <v>41.45920555034281</v>
+        <v>46.89317909334891</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.87101550231194</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>203.8540203006247</v>
+        <v>171.2158178729395</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -2422,7 +2422,7 @@
         <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>168.6495293740383</v>
+        <v>136.1045929782565</v>
       </c>
       <c r="D8" t="n">
         <v>29.12354564648163</v>
@@ -2436,10 +2436,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>97.07030425740334</v>
+        <v>81.20624310447914</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.445533531278805</v>
+        <v>2.176534660315179</v>
       </c>
       <c r="C2" t="n">
-        <v>5.433973543006096</v>
+        <v>3.272165098254619</v>
       </c>
       <c r="D2" t="n">
-        <v>9.928414533047993</v>
+        <v>12.90409182462007</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.06906649666254</v>
+        <v>17.42111301185965</v>
       </c>
       <c r="C3" t="n">
-        <v>40.81616080406114</v>
+        <v>32.55475387282424</v>
       </c>
       <c r="D3" t="n">
-        <v>58.22745633887833</v>
+        <v>85.59858233327941</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.26638208968293</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="C4" t="n">
-        <v>133.1534593792906</v>
+        <v>130.8689324715083</v>
       </c>
       <c r="D4" t="n">
-        <v>98.78345400131406</v>
+        <v>147.983740199643</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.47254910757476</v>
+        <v>40.2761995667254</v>
       </c>
       <c r="C5" t="n">
-        <v>253.3154513882833</v>
+        <v>250.6892762794231</v>
       </c>
       <c r="D5" t="n">
-        <v>75.59457322700442</v>
+        <v>102.3962855529423</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.27553661419064</v>
+        <v>30.06798693796707</v>
       </c>
       <c r="C6" t="n">
-        <v>248.4332200550639</v>
+        <v>230.8432464380738</v>
       </c>
       <c r="D6" t="n">
-        <v>41.41895389446869</v>
+        <v>46.249152599363</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>214.8731565330909</v>
+        <v>177.7434583584765</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>121.0838531032803</v>
+        <v>99.80447161373074</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.566689409528662</v>
+        <v>2.502474898125119</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5553093477052</v>
+        <v>2.740057842552848</v>
       </c>
       <c r="D2" t="n">
-        <v>13.6050596854523</v>
+        <v>10.84045815029328</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.45485228670254</v>
+        <v>12.59582304548658</v>
       </c>
       <c r="C3" t="n">
-        <v>31.02322745419921</v>
+        <v>22.84526907782328</v>
       </c>
       <c r="D3" t="n">
-        <v>53.30399160208057</v>
+        <v>77.28317927830892</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.8414652601933</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="C4" t="n">
-        <v>119.2038062496477</v>
+        <v>107.2834256246829</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8502539029318</v>
+        <v>154.9266599640764</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.59651136021713</v>
+        <v>48.76831720846032</v>
       </c>
       <c r="C5" t="n">
-        <v>251.6464802910637</v>
+        <v>248.2839944040184</v>
       </c>
       <c r="D5" t="n">
-        <v>89.75628386076465</v>
+        <v>125.5164439879547</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>39.1246095096439</v>
       </c>
       <c r="C6" t="n">
-        <v>316.0157502677101</v>
+        <v>303.7389952261037</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>62.43031826075894</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>16.5287043486993</v>
       </c>
       <c r="C7" t="n">
-        <v>278.1134166498534</v>
+        <v>244.4571418528643</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>184.5047547976243</v>
+        <v>152.3770611761474</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>74.88280614142545</v>
+        <v>64.5656195174957</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.347358760854124</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C2" t="n">
-        <v>4.197953183359361</v>
+        <v>2.744966581074082</v>
       </c>
       <c r="D2" t="n">
-        <v>9.63094497866121</v>
+        <v>8.128870991163589</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.9590696960579</v>
+        <v>11.02993545721291</v>
       </c>
       <c r="C3" t="n">
-        <v>25.70215489718149</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="D3" t="n">
-        <v>52.13571183402686</v>
+        <v>70.61711236647307</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.80844569114741</v>
+        <v>33.11925880276615</v>
       </c>
       <c r="C4" t="n">
-        <v>104.2076100672777</v>
+        <v>88.71366779885453</v>
       </c>
       <c r="D4" t="n">
-        <v>106.0199163293173</v>
+        <v>157.4409158346525</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.96528864411543</v>
+        <v>53.03891972193394</v>
       </c>
       <c r="C5" t="n">
-        <v>248.3085380966246</v>
+        <v>238.1474493576701</v>
       </c>
       <c r="D5" t="n">
-        <v>100.3591590666302</v>
+        <v>142.3043297305752</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.88688769649593</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="C6" t="n">
-        <v>357.3139491945564</v>
+        <v>346.4460021085442</v>
       </c>
       <c r="D6" t="n">
-        <v>60.0554705641859</v>
+        <v>73.90204018488291</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.39085875947725</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>340.335604397312</v>
+        <v>307.877061799504</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>231.8200854037993</v>
+        <v>194.4351328260808</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>81.87186804795849</v>
+        <v>71.1109314617092</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.316744655573225</v>
+        <v>2.650718801466388</v>
       </c>
       <c r="C2" t="n">
-        <v>6.530585728649783</v>
+        <v>3.344814428368883</v>
       </c>
       <c r="D2" t="n">
-        <v>9.326603190344699</v>
+        <v>13.88485778116264</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.57342277473815</v>
+        <v>8.654106012935634</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3628300444106</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="D3" t="n">
-        <v>48.43452298901639</v>
+        <v>62.8514880258808</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.34149363682442</v>
+        <v>27.49089921431918</v>
       </c>
       <c r="C4" t="n">
-        <v>86.96517513759096</v>
+        <v>69.82484196914589</v>
       </c>
       <c r="D4" t="n">
-        <v>106.7601540983194</v>
+        <v>156.1646438191316</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.44987109938586</v>
+        <v>52.15534678811181</v>
       </c>
       <c r="C5" t="n">
-        <v>224.7220495020949</v>
+        <v>207.2469403665017</v>
       </c>
       <c r="D5" t="n">
-        <v>109.2439757900639</v>
+        <v>156.6378462125786</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.21898046243861</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>372.6498300825958</v>
+        <v>359.7290485470036</v>
       </c>
       <c r="D6" t="n">
-        <v>72.33222560579226</v>
+        <v>92.82031844571895</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>27.12863431145211</v>
       </c>
       <c r="C7" t="n">
-        <v>407.6481539912903</v>
+        <v>380.9387259495516</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>48.62792728675301</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>314.7679489356123</v>
+        <v>274.3788483828986</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>150.5421747169101</v>
+        <v>127.9109266386126</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.713771638716436</v>
+        <v>6.056401587498573</v>
       </c>
       <c r="C2" t="n">
-        <v>12.1285111382651</v>
+        <v>8.81511263643211</v>
       </c>
       <c r="D2" t="n">
-        <v>5.484042675922683</v>
+        <v>5.518403845571321</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.151410130632261</v>
+        <v>1.936988220478957</v>
       </c>
       <c r="C2" t="n">
-        <v>3.865140711619692</v>
+        <v>1.97920337176157</v>
       </c>
       <c r="D2" t="n">
-        <v>6.938992773616455</v>
+        <v>10.33093109178918</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.30897278939726</v>
+        <v>11.83987731321653</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9770442543706</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="D3" t="n">
-        <v>52.25843029705771</v>
+        <v>68.83524028326511</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.18980576875168</v>
+        <v>39.09221183540375</v>
       </c>
       <c r="C4" t="n">
-        <v>126.1722514543916</v>
+        <v>104.4373390300714</v>
       </c>
       <c r="D4" t="n">
-        <v>107.9215616324434</v>
+        <v>157.4664412749629</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.02322745419922</v>
+        <v>30.80233422074368</v>
       </c>
       <c r="C5" t="n">
-        <v>322.8231888489574</v>
+        <v>307.5570120479196</v>
       </c>
       <c r="D5" t="n">
-        <v>100.6782270705104</v>
+        <v>141.0526014076605</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.22770871412303</v>
+        <v>16.82519215538184</v>
       </c>
       <c r="C6" t="n">
-        <v>334.209498722812</v>
+        <v>314.3654323768712</v>
       </c>
       <c r="D6" t="n">
-        <v>60.49823877880121</v>
+        <v>72.73474216453346</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>221.3409104086689</v>
+        <v>192.9546572880766</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>110.9031294102409</v>
+        <v>94.21341843804515</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>19.07535789351553</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.517823008494575</v>
+        <v>6.094689747964199</v>
       </c>
       <c r="C2" t="n">
-        <v>7.500552460445631</v>
+        <v>6.768168673077511</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5271007061893</v>
+        <v>8.6491972744144</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.13931036301181</v>
+        <v>12.86580366415445</v>
       </c>
       <c r="C3" t="n">
-        <v>30.56180603320321</v>
+        <v>22.21204180858409</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7410806479861</v>
+        <v>7.770533079113505</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39799740530968</v>
+        <v>13.39850177631349</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14245700426832</v>
+        <v>70.14509753481765</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576234988859962</v>
+        <v>1.576294326625116</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.912665512051039</v>
+        <v>3.999640147101506</v>
       </c>
       <c r="C2" t="n">
-        <v>10.61465617831651</v>
+        <v>7.33758234154066</v>
       </c>
       <c r="D2" t="n">
-        <v>11.34605821798039</v>
+        <v>12.97968639784708</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.36359080793659</v>
+        <v>17.8039946165159</v>
       </c>
       <c r="C3" t="n">
-        <v>29.74204670015712</v>
+        <v>24.82839944040184</v>
       </c>
       <c r="D3" t="n">
-        <v>16.3902779224005</v>
+        <v>13.15541923690726</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.14109393197106</v>
+        <v>14.9579080219044</v>
       </c>
       <c r="C4" t="n">
-        <v>47.10720009287471</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="D4" t="n">
-        <v>19.13131751265759</v>
+        <v>19.1440802328128</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43959415308325</v>
+        <v>15.44253134435044</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13668316983291</v>
+        <v>86.15306960532352</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250440874333317</v>
+        <v>3.251059230389567</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.78307481509046</v>
+        <v>4.234277848416493</v>
       </c>
       <c r="C2" t="n">
-        <v>5.250386722311942</v>
+        <v>4.740859663807847</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58520374718911</v>
+        <v>21.09775816426395</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.60764507566654</v>
+        <v>15.57542732787565</v>
       </c>
       <c r="C3" t="n">
-        <v>37.04134088123216</v>
+        <v>27.0864191601695</v>
       </c>
       <c r="D3" t="n">
-        <v>21.66226309420587</v>
+        <v>20.4841658491097</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.31672896004</v>
+        <v>25.94661007553895</v>
       </c>
       <c r="C4" t="n">
-        <v>62.4990406000562</v>
+        <v>50.74457533710914</v>
       </c>
       <c r="D4" t="n">
-        <v>23.04947260030661</v>
+        <v>21.44136986075034</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.41910845872215</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="C5" t="n">
-        <v>51.88536616944394</v>
+        <v>38.48451000647497</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>29.32971266437347</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7298999346087</v>
+        <v>16.73741838502854</v>
       </c>
       <c r="C21" t="n">
-        <v>102.052389601113</v>
+        <v>102.0982521486741</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182474983652174</v>
+        <v>5.021225515508564</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.973533869714341</v>
+        <v>4.603414985213294</v>
       </c>
       <c r="C2" t="n">
-        <v>7.750898125028567</v>
+        <v>6.885978397587128</v>
       </c>
       <c r="D2" t="n">
-        <v>15.18174649847268</v>
+        <v>29.25608158655495</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>14.99128744384879</v>
       </c>
       <c r="C3" t="n">
-        <v>27.40548716404971</v>
+        <v>22.05987091442583</v>
       </c>
       <c r="D3" t="n">
-        <v>24.88730430265664</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.27317220815464</v>
+        <v>28.37152690502857</v>
       </c>
       <c r="C4" t="n">
-        <v>79.37135664524189</v>
+        <v>60.2655645728947</v>
       </c>
       <c r="D4" t="n">
-        <v>28.4098150654942</v>
+        <v>26.58474608329938</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.94268308472197</v>
+        <v>25.99177046993431</v>
       </c>
       <c r="C5" t="n">
-        <v>86.19744843286996</v>
+        <v>67.93694113387929</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90050899116836</v>
+        <v>30.2132855981956</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27046364475338</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>48.3422387048172</v>
+        <v>37.91705983342032</v>
       </c>
       <c r="D6" t="n">
         <v>38.07806645691679</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05055599818976</v>
+        <v>18.06410027737903</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7583891310475</v>
+        <v>117.8467494286156</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016851999396587</v>
+        <v>6.881562010430107</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.407867265618932</v>
+        <v>6.91935781953152</v>
       </c>
       <c r="C2" t="n">
-        <v>9.210756961243575</v>
+        <v>12.89132910446487</v>
       </c>
       <c r="D2" t="n">
-        <v>18.89177107282137</v>
+        <v>29.32676742126072</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2219981543468</v>
+        <v>13.72974164389164</v>
       </c>
       <c r="C3" t="n">
-        <v>27.12568906833937</v>
+        <v>23.24778563656447</v>
       </c>
       <c r="D3" t="n">
-        <v>29.05973204570559</v>
+        <v>44.29154767709485</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.74316731658161</v>
+        <v>20.7777084126795</v>
       </c>
       <c r="C4" t="n">
-        <v>60.72502249848221</v>
+        <v>48.03887866420492</v>
       </c>
       <c r="D4" t="n">
-        <v>29.77542612210151</v>
+        <v>31.48563062289946</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.74571164906685</v>
+        <v>21.20575041173111</v>
       </c>
       <c r="C5" t="n">
-        <v>88.11185645615124</v>
+        <v>67.29880512611886</v>
       </c>
       <c r="D5" t="n">
-        <v>27.34167356327368</v>
+        <v>26.4090132442392</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.63901994447344</v>
+        <v>12.84027822384404</v>
       </c>
       <c r="C6" t="n">
-        <v>63.1950997223672</v>
+        <v>50.47557646614552</v>
       </c>
       <c r="D6" t="n">
-        <v>30.59125846433062</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>29.34443887993716</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051986797915499</v>
+        <v>7.059957610375389</v>
       </c>
       <c r="C21" t="n">
-        <v>66.1123762304578</v>
+        <v>66.18710259726927</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407491748697187</v>
+        <v>5.294968207781542</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.782093067386213</v>
+        <v>5.581235698643117</v>
       </c>
       <c r="C2" t="n">
-        <v>10.19446816089888</v>
+        <v>7.012623851434967</v>
       </c>
       <c r="D2" t="n">
-        <v>15.36533331916683</v>
+        <v>34.37884110731481</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.55150553007523</v>
+        <v>20.16509784522949</v>
       </c>
       <c r="C3" t="n">
-        <v>32.84436944557704</v>
+        <v>40.74252972624263</v>
       </c>
       <c r="D3" t="n">
-        <v>37.90527886096935</v>
+        <v>58.22254760035709</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.01867856857647</v>
+        <v>24.78520254141498</v>
       </c>
       <c r="C4" t="n">
-        <v>65.38341535513332</v>
+        <v>54.53510322320607</v>
       </c>
       <c r="D4" t="n">
-        <v>37.80317709972768</v>
+        <v>47.0944373727195</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.23153789394879</v>
+        <v>27.34167356327368</v>
       </c>
       <c r="C5" t="n">
-        <v>103.0589652533089</v>
+        <v>79.93880681829654</v>
       </c>
       <c r="D5" t="n">
-        <v>32.5203927031756</v>
+        <v>32.47130531796326</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.29941735426205</v>
+        <v>21.89690079552086</v>
       </c>
       <c r="C6" t="n">
-        <v>108.4379609248772</v>
+        <v>84.32721905627979</v>
       </c>
       <c r="D6" t="n">
-        <v>32.88560284915541</v>
+        <v>32.4428346345401</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>65.45606468524758</v>
+        <v>53.17930964364123</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>30.62561963397925</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.271948380518102</v>
+        <v>7.282324849643797</v>
       </c>
       <c r="C21" t="n">
-        <v>75.44646444787531</v>
+        <v>75.5541203150544</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453961285388576</v>
+        <v>6.372034243438322</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.924446484502001</v>
+        <v>4.425718650744621</v>
       </c>
       <c r="C2" t="n">
-        <v>9.085093255099984</v>
+        <v>8.957466053547897</v>
       </c>
       <c r="D2" t="n">
-        <v>22.55270826195773</v>
+        <v>32.6588191294744</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.84326452468578</v>
+        <v>19.69876768571225</v>
       </c>
       <c r="C3" t="n">
-        <v>36.8891699870739</v>
+        <v>32.58420630395164</v>
       </c>
       <c r="D3" t="n">
-        <v>41.400300688088</v>
+        <v>72.21736112439537</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.97886888105885</v>
+        <v>33.06820792214531</v>
       </c>
       <c r="C4" t="n">
-        <v>75.15965899402306</v>
+        <v>82.51098580342317</v>
       </c>
       <c r="D4" t="n">
-        <v>48.3068957874643</v>
+        <v>65.67695791870312</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.63744166415923</v>
+        <v>32.71674224402496</v>
       </c>
       <c r="C5" t="n">
-        <v>112.1155878249858</v>
+        <v>91.91612881010764</v>
       </c>
       <c r="D5" t="n">
-        <v>38.85266539556753</v>
+        <v>41.74882112309562</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.43654323768712</v>
+        <v>30.3497485290859</v>
       </c>
       <c r="C6" t="n">
-        <v>139.1499743568302</v>
+        <v>108.035444366136</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>115.2218375612226</v>
+        <v>90.12934798837841</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>60.8339964936536</v>
+        <v>50.90361846519712</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47834834358587</v>
+        <v>7.49065225561105</v>
       </c>
       <c r="C21" t="n">
-        <v>84.13141886534105</v>
+        <v>85.2061694075757</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543554800637637</v>
+        <v>7.49065225561105</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_85_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497637757489</v>
+        <v>10.84497638418623</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907209996481</v>
+        <v>37.78907212300185</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.496224559001145</v>
+        <v>4.52782041198629</v>
       </c>
       <c r="C2" t="n">
-        <v>14.10378751920968</v>
+        <v>12.64491043069892</v>
       </c>
       <c r="D2" t="n">
-        <v>28.98119222936584</v>
+        <v>25.12586899478862</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19531103988288</v>
+        <v>15.54597489674824</v>
       </c>
       <c r="C3" t="n">
-        <v>33.7328511179204</v>
+        <v>22.41330008795468</v>
       </c>
       <c r="D3" t="n">
-        <v>80.36095833112267</v>
+        <v>82.06429059799088</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.68456555396306</v>
+        <v>31.01340997715674</v>
       </c>
       <c r="C4" t="n">
-        <v>81.93666339643879</v>
+        <v>72.5305386420501</v>
       </c>
       <c r="D4" t="n">
-        <v>84.14461398328987</v>
+        <v>113.6775484224424</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.81616080406115</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="C5" t="n">
-        <v>123.3075116533994</v>
+        <v>119.5523266846554</v>
       </c>
       <c r="D5" t="n">
-        <v>55.07604620824608</v>
+        <v>81.55869053030378</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.35353665118265</v>
+        <v>38.31957639216151</v>
       </c>
       <c r="C6" t="n">
-        <v>126.3499477888603</v>
+        <v>132.7499610728452</v>
       </c>
       <c r="D6" t="n">
-        <v>40.25165587411923</v>
+        <v>52.1258943569844</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.90716024091983</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="C7" t="n">
-        <v>123.9652826152447</v>
+        <v>117.0184358599943</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>40.18391528252619</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>84.78373173875454</v>
+        <v>78.1912959047372</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>43.82030877905637</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.683216267696436</v>
+        <v>7.660742597812408</v>
       </c>
       <c r="C21" t="n">
-        <v>94.11939927928132</v>
+        <v>92.88650399847543</v>
       </c>
       <c r="D21" t="n">
-        <v>8.64361830115849</v>
+        <v>7.660742597812408</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.755005042294803</v>
+        <v>5.319109061609218</v>
       </c>
       <c r="C2" t="n">
-        <v>11.20272305316035</v>
+        <v>12.20803270230909</v>
       </c>
       <c r="D2" t="n">
-        <v>26.39526877637974</v>
+        <v>24.160811001514</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29625112697106</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="C3" t="n">
-        <v>44.15901173702153</v>
+        <v>35.75525138866883</v>
       </c>
       <c r="D3" t="n">
-        <v>83.7381704337317</v>
+        <v>83.26202279717199</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>29.89029060349839</v>
       </c>
       <c r="C4" t="n">
-        <v>82.94491828870026</v>
+        <v>64.3113468620958</v>
       </c>
       <c r="D4" t="n">
-        <v>101.9486085998058</v>
+        <v>124.4365215132832</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.16668579220627</v>
+        <v>42.63239405691775</v>
       </c>
       <c r="C5" t="n">
-        <v>135.0148530265426</v>
+        <v>124.9028516728005</v>
       </c>
       <c r="D5" t="n">
-        <v>69.26230053461248</v>
+        <v>100.1137221405685</v>
       </c>
     </row>
     <row r="6">
@@ -1150,10 +1150,10 @@
         <v>45.24286120251001</v>
       </c>
       <c r="C6" t="n">
-        <v>158.6317757999039</v>
+        <v>159.3965572615122</v>
       </c>
       <c r="D6" t="n">
-        <v>47.37619896383834</v>
+        <v>62.67182819600364</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.81219275551515</v>
       </c>
       <c r="C7" t="n">
-        <v>150.2555043872701</v>
+        <v>150.4950508271063</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.03041848329842</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="C8" t="n">
-        <v>120.9169559935584</v>
+        <v>113.9072773852362</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>73.77343123562655</v>
+        <v>67.44999427257284</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.859072271496631</v>
+        <v>7.83493613634488</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1679395294562</v>
+        <v>100.8748027554403</v>
       </c>
       <c r="D21" t="n">
-        <v>9.823840339370788</v>
+        <v>8.814303153387991</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.775040907007239</v>
+        <v>6.656249434793374</v>
       </c>
       <c r="C2" t="n">
-        <v>13.19272564966864</v>
+        <v>7.667449570167589</v>
       </c>
       <c r="D2" t="n">
-        <v>33.13202152292136</v>
+        <v>26.98922613744907</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.87409961414493</v>
+        <v>16.12029730373262</v>
       </c>
       <c r="C3" t="n">
-        <v>43.45215338996383</v>
+        <v>40.70325981807276</v>
       </c>
       <c r="D3" t="n">
-        <v>84.16523068507905</v>
+        <v>82.43735472560468</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.43381897875263</v>
+        <v>28.89479843139213</v>
       </c>
       <c r="C4" t="n">
-        <v>93.88256946171398</v>
+        <v>74.4577093854866</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5326506728414</v>
+        <v>132.7067641738583</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.27744335633691</v>
+        <v>43.61414176116455</v>
       </c>
       <c r="C5" t="n">
-        <v>141.0035140224482</v>
+        <v>120.5831617741145</v>
       </c>
       <c r="D5" t="n">
-        <v>85.41205026947252</v>
+        <v>117.0979574240383</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.76362945411734</v>
+        <v>49.95230493978197</v>
       </c>
       <c r="C6" t="n">
-        <v>182.5412593891307</v>
+        <v>176.3022527286422</v>
       </c>
       <c r="D6" t="n">
-        <v>55.18502020341747</v>
+        <v>74.86807992586176</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.75903951076558</v>
+        <v>42.99858595060179</v>
       </c>
       <c r="C7" t="n">
-        <v>182.2948407153647</v>
+        <v>182.8937068149553</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>51.3228247349105</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="C8" t="n">
-        <v>153.4618923893402</v>
+        <v>149.2894646462912</v>
       </c>
       <c r="D8" t="n">
-        <v>39.38771789438203</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>106.0562409943744</v>
+        <v>98.6234291255218</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>60.21549543997811</v>
+        <v>56.51430659496764</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>38.38240824523329</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.01805388975732</v>
+        <v>7.993492513022723</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2459842479435</v>
+        <v>107.9121489258067</v>
       </c>
       <c r="D21" t="n">
-        <v>11.02482409841632</v>
+        <v>9.991865641278403</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.295948027334795</v>
+        <v>6.073091298470769</v>
       </c>
       <c r="C2" t="n">
-        <v>9.18130453011617</v>
+        <v>5.274930414918113</v>
       </c>
       <c r="D2" t="n">
-        <v>27.31320287985051</v>
+        <v>22.38188416141879</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.0219836645877</v>
+        <v>19.49260066782042</v>
       </c>
       <c r="C3" t="n">
-        <v>63.82341825308514</v>
+        <v>55.46383655142355</v>
       </c>
       <c r="D3" t="n">
-        <v>90.28642762105792</v>
+        <v>90.8607500280423</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.18986252201391</v>
+        <v>20.9436237746972</v>
       </c>
       <c r="C4" t="n">
-        <v>120.8501971496696</v>
+        <v>100.2128786586974</v>
       </c>
       <c r="D4" t="n">
-        <v>105.4583566424881</v>
+        <v>128.7120327652781</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.15790681613028</v>
+        <v>28.12707172667112</v>
       </c>
       <c r="C5" t="n">
-        <v>109.0721699418207</v>
+        <v>105.3415286656828</v>
       </c>
       <c r="D5" t="n">
-        <v>55.93507544946203</v>
+        <v>76.20816554215867</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.52584122104457</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="C6" t="n">
-        <v>120.0706894724977</v>
+        <v>120.4329543753648</v>
       </c>
       <c r="D6" t="n">
-        <v>28.94094057349173</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>107.9156711462179</v>
+        <v>104.9812272582242</v>
       </c>
       <c r="D7" t="n">
-        <v>27.66761380108361</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>78.10784734987622</v>
+        <v>72.68369128391259</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>45.92812110007426</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.878885179479147</v>
+        <v>3.839615271309276</v>
       </c>
       <c r="C2" t="n">
-        <v>4.461061568097507</v>
+        <v>2.491675673378405</v>
       </c>
       <c r="D2" t="n">
-        <v>19.8362123643068</v>
+        <v>16.28523091804609</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.96307880233289</v>
+        <v>20.59706683509808</v>
       </c>
       <c r="C3" t="n">
-        <v>50.83489612589984</v>
+        <v>38.76921684070655</v>
       </c>
       <c r="D3" t="n">
-        <v>92.24501429103032</v>
+        <v>89.35867604054468</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.84298678724529</v>
+        <v>27.8099672181994</v>
       </c>
       <c r="C4" t="n">
-        <v>142.1511770887127</v>
+        <v>120.8629598698248</v>
       </c>
       <c r="D4" t="n">
-        <v>121.8712147620863</v>
+        <v>141.5130410809522</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.81491701444964</v>
+        <v>30.82687791334985</v>
       </c>
       <c r="C5" t="n">
-        <v>161.742934274662</v>
+        <v>143.433339590459</v>
       </c>
       <c r="D5" t="n">
-        <v>74.17103905584653</v>
+        <v>97.46300333910213</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.19503330244241</v>
+        <v>31.55729820530948</v>
       </c>
       <c r="C6" t="n">
-        <v>147.1600538757799</v>
+        <v>144.1814313410951</v>
       </c>
       <c r="D6" t="n">
-        <v>34.85793398698726</v>
+        <v>42.22398701195107</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>134.3256661381613</v>
+        <v>133.7866866485298</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94330497952771</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>94.54721265748907</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>49.81093327037041</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.567671157232909</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C2" t="n">
-        <v>6.752460709809561</v>
+        <v>5.744205817548087</v>
       </c>
       <c r="D2" t="n">
-        <v>18.48238228015045</v>
+        <v>24.43668210640736</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09851892778995</v>
+        <v>16.80261195818416</v>
       </c>
       <c r="C3" t="n">
-        <v>33.32051708213675</v>
+        <v>23.68957210347553</v>
       </c>
       <c r="D3" t="n">
-        <v>86.98775533478863</v>
+        <v>82.27045761588272</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.43305821522663</v>
+        <v>33.38727592602553</v>
       </c>
       <c r="C4" t="n">
-        <v>135.7570542909532</v>
+        <v>108.7128502820663</v>
       </c>
       <c r="D4" t="n">
-        <v>137.4162079111303</v>
+        <v>152.0295224888441</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.99992755120455</v>
+        <v>35.80924751240241</v>
       </c>
       <c r="C5" t="n">
-        <v>208.7195619228719</v>
+        <v>181.4515194374167</v>
       </c>
       <c r="D5" t="n">
-        <v>96.50579932746149</v>
+        <v>121.3194725522996</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>36.14598697495907</v>
       </c>
       <c r="C6" t="n">
-        <v>196.7903455685689</v>
+        <v>184.3928355593402</v>
       </c>
       <c r="D6" t="n">
-        <v>46.89317909334891</v>
+        <v>58.56615929684348</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>171.2158178729395</v>
+        <v>169.0598999144135</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>136.1045929782565</v>
+        <v>131.4314739060417</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>81.20624310447914</v>
+        <v>76.76874348128355</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.176534660315179</v>
+        <v>2.630102099677205</v>
       </c>
       <c r="C2" t="n">
-        <v>3.272165098254619</v>
+        <v>2.732203860918873</v>
       </c>
       <c r="D2" t="n">
-        <v>12.90409182462007</v>
+        <v>17.0362679117949</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.42111301185965</v>
+        <v>17.40638679629595</v>
       </c>
       <c r="C3" t="n">
-        <v>32.55475387282424</v>
+        <v>24.65659359215864</v>
       </c>
       <c r="D3" t="n">
-        <v>85.59858233327941</v>
+        <v>84.57756472086271</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.8151790563569</v>
+        <v>36.89702396870788</v>
       </c>
       <c r="C4" t="n">
-        <v>130.8689324715083</v>
+        <v>101.9486085998058</v>
       </c>
       <c r="D4" t="n">
-        <v>147.983740199643</v>
+        <v>160.6443585936098</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.2761995667254</v>
+        <v>37.7236555356837</v>
       </c>
       <c r="C5" t="n">
-        <v>250.6892762794231</v>
+        <v>215.9599512416922</v>
       </c>
       <c r="D5" t="n">
-        <v>102.3962855529423</v>
+        <v>127.5535704742669</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.06798693796707</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="C6" t="n">
-        <v>230.8432464380738</v>
+        <v>218.0029682142298</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>56.83533809425636</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.384125394267761</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>177.7434583584765</v>
+        <v>175.7073136198686</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>99.80447161373074</v>
+        <v>95.2148010963769</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.502474898125119</v>
+        <v>2.476949457814702</v>
       </c>
       <c r="C2" t="n">
-        <v>2.740057842552848</v>
+        <v>8.685521939471531</v>
       </c>
       <c r="D2" t="n">
-        <v>10.84045815029328</v>
+        <v>19.92064266687203</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59582304548658</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="C3" t="n">
-        <v>22.84526907782328</v>
+        <v>17.66164119940012</v>
       </c>
       <c r="D3" t="n">
-        <v>77.28317927830892</v>
+        <v>79.78663592413828</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.61173629739955</v>
+        <v>35.08471770666826</v>
       </c>
       <c r="C4" t="n">
-        <v>107.2834256246829</v>
+        <v>82.38335860187109</v>
       </c>
       <c r="D4" t="n">
-        <v>154.9266599640764</v>
+        <v>164.8560562448286</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.76831720846032</v>
+        <v>45.20948178056562</v>
       </c>
       <c r="C5" t="n">
-        <v>248.2839944040184</v>
+        <v>204.7434837206723</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5164439879547</v>
+        <v>149.7901559754571</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.1246095096439</v>
+        <v>38.35982804803563</v>
       </c>
       <c r="C6" t="n">
-        <v>303.7389952261037</v>
+        <v>274.3552864379967</v>
       </c>
       <c r="D6" t="n">
-        <v>62.43031826075894</v>
+        <v>77.12217265481245</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>244.4571418528643</v>
+        <v>237.3306352677367</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>152.3770611761474</v>
+        <v>149.7901559754571</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>64.5656195174957</v>
+        <v>63.01249464937726</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.752419652080557</v>
+        <v>1.787762569433442</v>
       </c>
       <c r="C2" t="n">
-        <v>2.744966581074082</v>
+        <v>4.798782778358409</v>
       </c>
       <c r="D2" t="n">
-        <v>8.128870991163589</v>
+        <v>14.50630407795087</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.02993545721291</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C3" t="n">
-        <v>17.86780821729195</v>
+        <v>25.28982086139784</v>
       </c>
       <c r="D3" t="n">
-        <v>70.61711236647307</v>
+        <v>78.58890372495716</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.11925880276615</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C4" t="n">
-        <v>88.71366779885453</v>
+        <v>68.68895987533233</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4409158346525</v>
+        <v>166.7321761076443</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.03891972193394</v>
+        <v>49.40645321622075</v>
       </c>
       <c r="C5" t="n">
-        <v>238.1474493576701</v>
+        <v>190.3608798534566</v>
       </c>
       <c r="D5" t="n">
-        <v>142.3043297305752</v>
+        <v>165.768099862074</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.28311285838414</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="C6" t="n">
-        <v>346.4460021085442</v>
+        <v>304.2622667524673</v>
       </c>
       <c r="D6" t="n">
-        <v>73.90204018488291</v>
+        <v>90.64672902851652</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>307.877061799504</v>
+        <v>293.6839352392078</v>
       </c>
       <c r="D7" t="n">
-        <v>40.96244121199391</v>
+        <v>45.45393695892307</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>194.4351328260808</v>
+        <v>192.2654703996953</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>71.1109314617092</v>
+        <v>71.22186895228909</v>
       </c>
       <c r="D9" t="n">
         <v>31.94999728700819</v>
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>10.75504610002381</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.06233313145306</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.650718801466388</v>
+        <v>2.873575530330414</v>
       </c>
       <c r="C2" t="n">
-        <v>3.344814428368883</v>
+        <v>7.460300804571512</v>
       </c>
       <c r="D2" t="n">
-        <v>13.88485778116264</v>
+        <v>15.04430181987812</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.654106012935634</v>
+        <v>8.924086631603506</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5593184539802</v>
+        <v>22.08932334555324</v>
       </c>
       <c r="D3" t="n">
-        <v>62.8514880258808</v>
+        <v>73.58199043329844</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.49089921431918</v>
+        <v>27.10801760966293</v>
       </c>
       <c r="C4" t="n">
-        <v>69.82484196914589</v>
+        <v>66.04707680320416</v>
       </c>
       <c r="D4" t="n">
-        <v>156.1646438191316</v>
+        <v>165.1113106479328</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.15534678811181</v>
+        <v>49.21010367537139</v>
       </c>
       <c r="C5" t="n">
-        <v>207.2469403665017</v>
+        <v>163.4609927570939</v>
       </c>
       <c r="D5" t="n">
-        <v>156.6378462125786</v>
+        <v>181.5251505152353</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>52.5284109157256</v>
       </c>
       <c r="C6" t="n">
-        <v>359.7290485470036</v>
+        <v>304.7050349670826</v>
       </c>
       <c r="D6" t="n">
-        <v>92.82031844571895</v>
+        <v>112.1008616094221</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="C7" t="n">
-        <v>380.9387259495516</v>
+        <v>351.175080799901</v>
       </c>
       <c r="D7" t="n">
-        <v>48.62792728675301</v>
+        <v>55.45500082208532</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>274.3788483828986</v>
+        <v>268.4540009877691</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>127.9109266386126</v>
+        <v>129.6859264878909</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3697,7 +3697,7 @@
         <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.056401587498573</v>
+        <v>5.793293202760428</v>
       </c>
       <c r="C2" t="n">
-        <v>8.81511263643211</v>
+        <v>8.995754214013523</v>
       </c>
       <c r="D2" t="n">
-        <v>5.518403845571321</v>
+        <v>16.89882323320035</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.936988220478957</v>
+        <v>2.076396394482004</v>
       </c>
       <c r="C2" t="n">
-        <v>1.97920337176157</v>
+        <v>4.356014563743098</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33093109178918</v>
+        <v>11.19388732382213</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83987731321653</v>
+        <v>12.21294144083032</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5915362017711</v>
+        <v>27.35149104031614</v>
       </c>
       <c r="D3" t="n">
-        <v>68.83524028326511</v>
+        <v>79.11413874672922</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.09221183540375</v>
+        <v>37.25438013305371</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4373390300714</v>
+        <v>96.10328276872026</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4664412749629</v>
+        <v>170.0632460681537</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.80233422074368</v>
+        <v>30.48326621686347</v>
       </c>
       <c r="C5" t="n">
-        <v>307.5570120479196</v>
+        <v>251.0328879759095</v>
       </c>
       <c r="D5" t="n">
-        <v>141.0526014076605</v>
+        <v>164.8599832356456</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.82519215538184</v>
+        <v>16.78494049950772</v>
       </c>
       <c r="C6" t="n">
-        <v>314.3654323768712</v>
+        <v>288.0408494351972</v>
       </c>
       <c r="D6" t="n">
-        <v>72.73474216453346</v>
+        <v>85.5750203883775</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>192.9546572880766</v>
+        <v>188.7625945909427</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>94.21341843804515</v>
+        <v>95.54859531582082</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4305,7 +4305,7 @@
         <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.094689747964199</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C2" t="n">
-        <v>6.768168673077511</v>
+        <v>4.612250714551515</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6491972744144</v>
+        <v>19.94813160259094</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.86580366415445</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="C3" t="n">
-        <v>22.21204180858409</v>
+        <v>22.66855449105885</v>
       </c>
       <c r="D3" t="n">
-        <v>7.770533079113505</v>
+        <v>17.33275571847744</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39850177631349</v>
+        <v>13.39656465751588</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14509753481765</v>
+        <v>70.13495614817134</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576294326625116</v>
+        <v>1.576066430295985</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.999640147101506</v>
+        <v>4.237223091529233</v>
       </c>
       <c r="C2" t="n">
-        <v>7.33758234154066</v>
+        <v>7.267878254539137</v>
       </c>
       <c r="D2" t="n">
-        <v>12.97968639784708</v>
+        <v>20.10619298297468</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.8039946165159</v>
+        <v>17.83835578616454</v>
       </c>
       <c r="C3" t="n">
-        <v>24.82839944040184</v>
+        <v>19.73803759388213</v>
       </c>
       <c r="D3" t="n">
-        <v>13.15541923690726</v>
+        <v>29.89912633283661</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.9579080219044</v>
+        <v>14.33253473429918</v>
       </c>
       <c r="C4" t="n">
-        <v>34.37000537797658</v>
+        <v>35.09748042682347</v>
       </c>
       <c r="D4" t="n">
-        <v>19.1440802328128</v>
+        <v>24.15982925380975</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44253134435044</v>
+        <v>15.43688889004783</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15306960532352</v>
+        <v>86.12159064974054</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251059230389567</v>
+        <v>3.249871345273228</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.234277848416493</v>
+        <v>5.282784396552087</v>
       </c>
       <c r="C2" t="n">
-        <v>4.740859663807847</v>
+        <v>8.872054003278425</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09775816426395</v>
+        <v>37.02268767485146</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.57542732787565</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="C3" t="n">
-        <v>27.0864191601695</v>
+        <v>25.10819753611218</v>
       </c>
       <c r="D3" t="n">
-        <v>20.4841658491097</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.94661007553895</v>
+        <v>25.83174559414208</v>
       </c>
       <c r="C4" t="n">
-        <v>50.74457533710914</v>
+        <v>43.0614178036736</v>
       </c>
       <c r="D4" t="n">
-        <v>21.44136986075034</v>
+        <v>33.70634392990574</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.27813769993811</v>
+        <v>12.56637061435918</v>
       </c>
       <c r="C5" t="n">
-        <v>38.48451000647497</v>
+        <v>39.31899555508476</v>
       </c>
       <c r="D5" t="n">
-        <v>29.32971266437347</v>
+        <v>31.31775176547326</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73741838502854</v>
+        <v>16.72692220336727</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0982521486741</v>
+        <v>102.0342254405403</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021225515508564</v>
+        <v>4.181730550841817</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>4.73398742987812</v>
       </c>
       <c r="C2" t="n">
-        <v>6.885978397587128</v>
+        <v>6.403940274801944</v>
       </c>
       <c r="D2" t="n">
-        <v>29.25608158655495</v>
+        <v>30.62365613857076</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.99128744384879</v>
+        <v>17.10204500797944</v>
       </c>
       <c r="C3" t="n">
-        <v>22.05987091442583</v>
+        <v>30.36054775383261</v>
       </c>
       <c r="D3" t="n">
-        <v>31.96079651175491</v>
+        <v>58.4974369575462</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.37152690502857</v>
+        <v>28.46086594611503</v>
       </c>
       <c r="C4" t="n">
-        <v>60.2655645728947</v>
+        <v>53.47579745032376</v>
       </c>
       <c r="D4" t="n">
-        <v>26.58474608329938</v>
+        <v>45.03963942773092</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.99177046993431</v>
+        <v>25.64815877344793</v>
       </c>
       <c r="C5" t="n">
-        <v>67.93694113387929</v>
+        <v>61.04016351154545</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2132855981956</v>
+        <v>35.83379120500859</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>11.35096695650162</v>
       </c>
       <c r="C6" t="n">
-        <v>37.91705983342032</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.90042687571034</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06410027737903</v>
+        <v>18.04444781785013</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8467494286156</v>
+        <v>117.7185405259746</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881562010430107</v>
+        <v>6.014815939283376</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.91935781953152</v>
+        <v>5.182646130718912</v>
       </c>
       <c r="C2" t="n">
-        <v>12.89132910446487</v>
+        <v>10.3250406055637</v>
       </c>
       <c r="D2" t="n">
-        <v>29.32676742126072</v>
+        <v>33.18798114206342</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.72974164389164</v>
+        <v>14.70167187109599</v>
       </c>
       <c r="C3" t="n">
-        <v>23.24778563656447</v>
+        <v>25.56961895710818</v>
       </c>
       <c r="D3" t="n">
-        <v>44.29154767709485</v>
+        <v>64.69226497134358</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.7777084126795</v>
+        <v>22.32199755145973</v>
       </c>
       <c r="C4" t="n">
-        <v>48.03887866420492</v>
+        <v>54.62444226429253</v>
       </c>
       <c r="D4" t="n">
-        <v>31.48563062289946</v>
+        <v>55.16047651081129</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.20575041173111</v>
+        <v>20.83759502263855</v>
       </c>
       <c r="C5" t="n">
-        <v>67.29880512611886</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="D5" t="n">
-        <v>26.4090132442392</v>
+        <v>34.95021827118646</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.84027822384404</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>50.47557646614552</v>
+        <v>46.32965591111124</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.059957610375389</v>
+        <v>7.049026770172306</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18710259726927</v>
+        <v>66.08462597036537</v>
       </c>
       <c r="D21" t="n">
-        <v>5.294968207781542</v>
+        <v>4.405641731357691</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.581235698643117</v>
+        <v>4.975497365122835</v>
       </c>
       <c r="C2" t="n">
-        <v>7.012623851434967</v>
+        <v>5.896376711706344</v>
       </c>
       <c r="D2" t="n">
-        <v>34.37884110731481</v>
+        <v>25.83567258495906</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.16509784522949</v>
+        <v>16.78788574262046</v>
       </c>
       <c r="C3" t="n">
-        <v>40.74252972624263</v>
+        <v>34.93058331710152</v>
       </c>
       <c r="D3" t="n">
-        <v>58.22254760035709</v>
+        <v>76.93956758182253</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.78520254141498</v>
+        <v>26.43159344143688</v>
       </c>
       <c r="C4" t="n">
-        <v>54.53510322320607</v>
+        <v>60.53358169615408</v>
       </c>
       <c r="D4" t="n">
-        <v>47.0944373727195</v>
+        <v>76.27001564752621</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.34167356327368</v>
+        <v>28.10252803406495</v>
       </c>
       <c r="C5" t="n">
-        <v>79.93880681829654</v>
+        <v>84.25849671698251</v>
       </c>
       <c r="D5" t="n">
-        <v>32.47130531796326</v>
+        <v>47.19752088166541</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.89690079552086</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="C6" t="n">
-        <v>84.32721905627979</v>
+        <v>75.59260973159593</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.31856928226148</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>53.17930964364123</v>
+        <v>49.1669067763845</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.70353755551324</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282324849643797</v>
+        <v>7.266749610064815</v>
       </c>
       <c r="C21" t="n">
-        <v>75.5541203150544</v>
+        <v>75.39252720442246</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372034243438322</v>
+        <v>5.450062207548611</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.425718650744621</v>
+        <v>4.228387362191013</v>
       </c>
       <c r="C2" t="n">
-        <v>8.957466053547897</v>
+        <v>4.665265090580843</v>
       </c>
       <c r="D2" t="n">
-        <v>32.6588191294744</v>
+        <v>26.78305911955723</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69876768571225</v>
+        <v>16.98914402199105</v>
       </c>
       <c r="C3" t="n">
-        <v>32.58420630395164</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D3" t="n">
-        <v>72.21736112439537</v>
+        <v>79.75718349301087</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.06820792214531</v>
+        <v>29.77542612210151</v>
       </c>
       <c r="C4" t="n">
-        <v>82.51098580342317</v>
+        <v>76.12962572581891</v>
       </c>
       <c r="D4" t="n">
-        <v>65.67695791870312</v>
+        <v>97.71138550827655</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.71674224402496</v>
+        <v>34.63115026730624</v>
       </c>
       <c r="C5" t="n">
-        <v>91.91612881010764</v>
+        <v>99.77011044408214</v>
       </c>
       <c r="D5" t="n">
-        <v>41.74882112309562</v>
+        <v>63.88723185386119</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.3497485290859</v>
+        <v>30.30949687321178</v>
       </c>
       <c r="C6" t="n">
-        <v>108.035444366136</v>
+        <v>106.4253781311713</v>
       </c>
       <c r="D6" t="n">
-        <v>35.783722072092</v>
+        <v>42.58625191481815</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>90.12934798837841</v>
+        <v>81.98476903394689</v>
       </c>
       <c r="D7" t="n">
-        <v>35.15344004596554</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>50.90361846519712</v>
+        <v>47.56567627075796</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.06562253193106</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.49065225561105</v>
+        <v>7.471158657997735</v>
       </c>
       <c r="C21" t="n">
-        <v>85.2061694075757</v>
+        <v>84.05053490247452</v>
       </c>
       <c r="D21" t="n">
-        <v>7.49065225561105</v>
+        <v>6.537263825748019</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_85_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497638418623</v>
+        <v>10.84497629677739</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907212300185</v>
+        <v>37.78907181842775</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.52782041198629</v>
+        <v>0.8551022503989718</v>
       </c>
       <c r="C2" t="n">
-        <v>12.64491043069892</v>
+        <v>1.9546596791554</v>
       </c>
       <c r="D2" t="n">
-        <v>25.12586899478862</v>
+        <v>12.52808245389355</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.54597489674824</v>
+        <v>7.392560212978482</v>
       </c>
       <c r="C3" t="n">
-        <v>22.41330008795468</v>
+        <v>30.66488954214912</v>
       </c>
       <c r="D3" t="n">
-        <v>82.06429059799088</v>
+        <v>65.77218744601507</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.01340997715674</v>
+        <v>12.31602494977624</v>
       </c>
       <c r="C4" t="n">
-        <v>72.5305386420501</v>
+        <v>119.7781286566321</v>
       </c>
       <c r="D4" t="n">
-        <v>113.6775484224424</v>
+        <v>68.99526515905734</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.83441309981433</v>
+        <v>11.46190444708151</v>
       </c>
       <c r="C5" t="n">
-        <v>119.5523266846554</v>
+        <v>146.1086020845316</v>
       </c>
       <c r="D5" t="n">
-        <v>81.55869053030378</v>
+        <v>41.60155896745859</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>8.533351045313278</v>
       </c>
       <c r="C6" t="n">
-        <v>132.7499610728452</v>
+        <v>87.26558993509049</v>
       </c>
       <c r="D6" t="n">
-        <v>52.1258943569844</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.24840753137022</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>117.0184358599943</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>78.1912959047372</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>43.82030877905637</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660742597812408</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.88650399847543</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660742597812408</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.319109061609218</v>
+        <v>1.43727863901733</v>
       </c>
       <c r="C2" t="n">
-        <v>12.20803270230909</v>
+        <v>13.09356913153971</v>
       </c>
       <c r="D2" t="n">
-        <v>24.160811001514</v>
+        <v>16.91845818728528</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.36926030998382</v>
+        <v>5.006913291658734</v>
       </c>
       <c r="C3" t="n">
-        <v>35.75525138866883</v>
+        <v>17.11186248502191</v>
       </c>
       <c r="D3" t="n">
-        <v>83.26202279717199</v>
+        <v>60.66219064541041</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.89029060349839</v>
+        <v>13.50295792421063</v>
       </c>
       <c r="C4" t="n">
-        <v>64.3113468620958</v>
+        <v>96.51168981368694</v>
       </c>
       <c r="D4" t="n">
-        <v>124.4365215132832</v>
+        <v>85.49746231974197</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.63239405691775</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C5" t="n">
-        <v>124.9028516728005</v>
+        <v>188.1274038262951</v>
       </c>
       <c r="D5" t="n">
-        <v>100.1137221405685</v>
+        <v>56.05779391249288</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.24286120251001</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>159.3965572615122</v>
+        <v>160.9261201847287</v>
       </c>
       <c r="D6" t="n">
-        <v>62.67182819600364</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.81219275551515</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>150.4950508271063</v>
+        <v>86.95535766054849</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>113.9072773852362</v>
+        <v>45.98015372839936</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>67.44999427257284</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.07910495788326</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.83493613634488</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8748027554403</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.814303153387991</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.656249434793374</v>
+        <v>0.7588909753827844</v>
       </c>
       <c r="C2" t="n">
-        <v>7.667449570167589</v>
+        <v>5.469316460358981</v>
       </c>
       <c r="D2" t="n">
-        <v>26.98922613744907</v>
+        <v>11.55615222668921</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12029730373262</v>
+        <v>5.448699758569798</v>
       </c>
       <c r="C3" t="n">
-        <v>40.70325981807276</v>
+        <v>34.99439691787756</v>
       </c>
       <c r="D3" t="n">
-        <v>82.43735472560468</v>
+        <v>61.97773256910114</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.89479843139213</v>
+        <v>14.6516027381794</v>
       </c>
       <c r="C4" t="n">
-        <v>74.4577093854866</v>
+        <v>84.71893639027425</v>
       </c>
       <c r="D4" t="n">
-        <v>132.7067641738583</v>
+        <v>94.62280723071608</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.61414176116455</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C5" t="n">
-        <v>120.5831617741145</v>
+        <v>209.7994843975434</v>
       </c>
       <c r="D5" t="n">
-        <v>117.0979574240383</v>
+        <v>63.59270754258716</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.95230493978197</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>176.3022527286422</v>
+        <v>204.7199217757704</v>
       </c>
       <c r="D6" t="n">
-        <v>74.86807992586176</v>
+        <v>36.02523200733671</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.99858595060179</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>182.8937068149553</v>
+        <v>82.04465564390594</v>
       </c>
       <c r="D7" t="n">
-        <v>51.3228247349105</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.20561154301086</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>149.2894646462912</v>
+        <v>42.14152020479433</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>98.6234291255218</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>56.51430659496764</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.38240824523329</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.993492513022723</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9121489258067</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.991865641278403</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.073091298470769</v>
+        <v>0.4948008429403924</v>
       </c>
       <c r="C2" t="n">
-        <v>5.274930414918113</v>
+        <v>6.330309196983433</v>
       </c>
       <c r="D2" t="n">
-        <v>22.38188416141879</v>
+        <v>12.05684355585508</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.49260066782042</v>
+        <v>4.010439371848221</v>
       </c>
       <c r="C3" t="n">
-        <v>55.46383655142355</v>
+        <v>27.48402698038946</v>
       </c>
       <c r="D3" t="n">
-        <v>90.8607500280423</v>
+        <v>57.56968537703295</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.9436237746972</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2128786586974</v>
+        <v>87.0162260182118</v>
       </c>
       <c r="D4" t="n">
-        <v>128.7120327652781</v>
+        <v>103.2376433354818</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.12707172667112</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="C5" t="n">
-        <v>105.3415286656828</v>
+        <v>184.4949373205819</v>
       </c>
       <c r="D5" t="n">
-        <v>76.20816554215867</v>
+        <v>80.9696419077557</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.68684784454105</v>
+        <v>14.61135108230528</v>
       </c>
       <c r="C6" t="n">
-        <v>120.4329543753648</v>
+        <v>268.8810612391164</v>
       </c>
       <c r="D6" t="n">
-        <v>33.77113927838603</v>
+        <v>46.36990756698535</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>104.9812272582242</v>
+        <v>181.7558612257332</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>72.68369128391259</v>
+        <v>72.34989706446869</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.839615271309276</v>
+        <v>0.3328124717396687</v>
       </c>
       <c r="C2" t="n">
-        <v>2.491675673378405</v>
+        <v>3.965278977452867</v>
       </c>
       <c r="D2" t="n">
-        <v>16.28523091804609</v>
+        <v>9.600510799829559</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.59706683509808</v>
+        <v>3.023782929080176</v>
       </c>
       <c r="C3" t="n">
-        <v>38.76921684070655</v>
+        <v>26.6397239547372</v>
       </c>
       <c r="D3" t="n">
-        <v>89.35867604054468</v>
+        <v>55.17422097867075</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.8099672181994</v>
+        <v>11.09080381487622</v>
       </c>
       <c r="C4" t="n">
-        <v>120.8629598698248</v>
+        <v>80.68591682122836</v>
       </c>
       <c r="D4" t="n">
-        <v>141.5130410809522</v>
+        <v>107.7684089905809</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.82687791334985</v>
+        <v>19.75767254796706</v>
       </c>
       <c r="C5" t="n">
-        <v>143.433339590459</v>
+        <v>180.8133834296563</v>
       </c>
       <c r="D5" t="n">
-        <v>97.46300333910213</v>
+        <v>94.71410976721104</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>17.63022527286423</v>
       </c>
       <c r="C6" t="n">
-        <v>144.1814313410951</v>
+        <v>291.6232468079938</v>
       </c>
       <c r="D6" t="n">
-        <v>42.22398701195107</v>
+        <v>54.98376192404687</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7866866485298</v>
+        <v>256.1350307948801</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>94.54721265748907</v>
+        <v>115.0755571532899</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>48.36874589283183</v>
+        <v>48.25780840225195</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.422773407631881</v>
+        <v>0.4113522880794135</v>
       </c>
       <c r="C2" t="n">
-        <v>5.744205817548087</v>
+        <v>6.384305320717008</v>
       </c>
       <c r="D2" t="n">
-        <v>24.43668210640736</v>
+        <v>11.97044975788136</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.80261195818416</v>
+        <v>2.091122610045706</v>
       </c>
       <c r="C3" t="n">
-        <v>23.68957210347553</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D3" t="n">
-        <v>82.27045761588272</v>
+        <v>51.0165194511855</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.38727592602553</v>
+        <v>8.62759882492097</v>
       </c>
       <c r="C4" t="n">
-        <v>108.7128502820663</v>
+        <v>73.62813257539804</v>
       </c>
       <c r="D4" t="n">
-        <v>152.0295224888441</v>
+        <v>108.9298165247048</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.80924751240241</v>
+        <v>18.75138115111408</v>
       </c>
       <c r="C5" t="n">
-        <v>181.4515194374167</v>
+        <v>167.1916340332318</v>
       </c>
       <c r="D5" t="n">
-        <v>121.3194725522996</v>
+        <v>109.0967136344268</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>21.41388092503143</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3928355593402</v>
+        <v>290.9792203140079</v>
       </c>
       <c r="D6" t="n">
-        <v>58.56615929684348</v>
+        <v>68.66932492124741</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>12.6360747013607</v>
       </c>
       <c r="C7" t="n">
-        <v>169.0598999144135</v>
+        <v>331.6520459532489</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>131.4314739060417</v>
+        <v>207.4531073843935</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>76.76874348128355</v>
+        <v>86.64218014289374</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>43.15468383557703</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.630102099677205</v>
+        <v>0.2827433388230814</v>
       </c>
       <c r="C2" t="n">
-        <v>2.732203860918873</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0362679117949</v>
+        <v>8.714974370598936</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.40638679629595</v>
+        <v>2.969786805346601</v>
       </c>
       <c r="C3" t="n">
-        <v>24.65659359215864</v>
+        <v>25.40763058590746</v>
       </c>
       <c r="D3" t="n">
-        <v>84.57756472086271</v>
+        <v>55.69454726192155</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.89702396870788</v>
+        <v>13.3115171218825</v>
       </c>
       <c r="C4" t="n">
-        <v>101.9486085998058</v>
+        <v>101.8337441184089</v>
       </c>
       <c r="D4" t="n">
-        <v>160.6443585936098</v>
+        <v>110.8186991076757</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.7236555356837</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C5" t="n">
-        <v>215.9599512416922</v>
+        <v>247.6949457814703</v>
       </c>
       <c r="D5" t="n">
-        <v>127.5535704742669</v>
+        <v>100.7273144557228</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.18874190558942</v>
+        <v>7.808821239579131</v>
       </c>
       <c r="C6" t="n">
-        <v>218.0029682142298</v>
+        <v>286.8735514148478</v>
       </c>
       <c r="D6" t="n">
-        <v>56.83533809425636</v>
+        <v>59.57245069369646</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>175.7073136198686</v>
+        <v>145.883781860259</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>95.2148010963769</v>
+        <v>63.83814446864884</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.476949457814702</v>
+        <v>0.2061670178918302</v>
       </c>
       <c r="C2" t="n">
-        <v>8.685521939471531</v>
+        <v>2.114684554947629</v>
       </c>
       <c r="D2" t="n">
-        <v>19.92064266687203</v>
+        <v>6.573782627636643</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.40085616296896</v>
+        <v>1.968404147014855</v>
       </c>
       <c r="C3" t="n">
-        <v>17.66164119940012</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D3" t="n">
-        <v>79.78663592413828</v>
+        <v>49.95623193059895</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.08471770666826</v>
+        <v>8.997717709422018</v>
       </c>
       <c r="C4" t="n">
-        <v>82.38335860187109</v>
+        <v>79.52450928710439</v>
       </c>
       <c r="D4" t="n">
-        <v>164.8560562448286</v>
+        <v>109.6062406929309</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.20948178056562</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>204.7434837206723</v>
+        <v>198.3866673356742</v>
       </c>
       <c r="D5" t="n">
-        <v>149.7901559754571</v>
+        <v>103.353489564583</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.35982804803563</v>
+        <v>7.607562960208536</v>
       </c>
       <c r="C6" t="n">
-        <v>274.3552864379967</v>
+        <v>276.2873659199544</v>
       </c>
       <c r="D6" t="n">
-        <v>77.12217265481245</v>
+        <v>62.63157654012953</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C7" t="n">
-        <v>237.3306352677367</v>
+        <v>189.3015740805742</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>149.7901559754571</v>
+        <v>75.27059648460295</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>17.65182372235765</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.787762569433442</v>
+        <v>0.06283185307179587</v>
       </c>
       <c r="C2" t="n">
-        <v>4.798782778358409</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="D2" t="n">
-        <v>14.50630407795087</v>
+        <v>8.426340545550373</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.47172192412398</v>
+        <v>1.276272015520854</v>
       </c>
       <c r="C3" t="n">
-        <v>25.28982086139784</v>
+        <v>12.61545799957151</v>
       </c>
       <c r="D3" t="n">
-        <v>78.58890372495716</v>
+        <v>43.83994373314132</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>6.330309196983433</v>
       </c>
       <c r="C4" t="n">
-        <v>68.68895987533233</v>
+        <v>61.22276858453534</v>
       </c>
       <c r="D4" t="n">
-        <v>166.7321761076443</v>
+        <v>109.9635968572767</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.40645321622075</v>
+        <v>13.44994354818131</v>
       </c>
       <c r="C5" t="n">
-        <v>190.3608798534566</v>
+        <v>172.1494599396782</v>
       </c>
       <c r="D5" t="n">
-        <v>165.768099862074</v>
+        <v>118.7669285212579</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.59883470852411</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="C6" t="n">
-        <v>304.2622667524673</v>
+        <v>297.7817501567341</v>
       </c>
       <c r="D6" t="n">
-        <v>90.64672902851652</v>
+        <v>79.21525876026665</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.03153909972291</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>293.6839352392078</v>
+        <v>299.7324828450724</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>192.2654703996953</v>
+        <v>162.7246819789088</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22186895228909</v>
+        <v>60.79374483777947</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.873575530330414</v>
+        <v>0.1452986602285279</v>
       </c>
       <c r="C2" t="n">
-        <v>7.460300804571512</v>
+        <v>7.954119899807657</v>
       </c>
       <c r="D2" t="n">
-        <v>15.04430181987812</v>
+        <v>9.383544557191014</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.924086631603506</v>
+        <v>0.7264933011426398</v>
       </c>
       <c r="C3" t="n">
-        <v>22.08932334555324</v>
+        <v>26.81152980298039</v>
       </c>
       <c r="D3" t="n">
-        <v>73.58199043329844</v>
+        <v>40.57563261652067</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.10801760966293</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="C4" t="n">
-        <v>66.04707680320416</v>
+        <v>45.7543517564226</v>
       </c>
       <c r="D4" t="n">
-        <v>165.1113106479328</v>
+        <v>107.3089510649934</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.21010367537139</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C5" t="n">
-        <v>163.4609927570939</v>
+        <v>142.427048193606</v>
       </c>
       <c r="D5" t="n">
-        <v>181.5251505152353</v>
+        <v>130.2779203535518</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.5284109157256</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C6" t="n">
-        <v>304.7050349670826</v>
+        <v>287.6785845323301</v>
       </c>
       <c r="D6" t="n">
-        <v>112.1008616094221</v>
+        <v>95.11466283054375</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.06874770149305</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>351.175080799901</v>
+        <v>361.2360312730223</v>
       </c>
       <c r="D7" t="n">
-        <v>55.45500082208532</v>
+        <v>53.71828913327272</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>268.4540009877691</v>
+        <v>275.0464368217864</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>129.6859264878909</v>
+        <v>126.2468642799143</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.51718541815559</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.793293202760428</v>
+        <v>2.743984833369835</v>
       </c>
       <c r="C2" t="n">
-        <v>8.995754214013523</v>
+        <v>10.9101622372948</v>
       </c>
       <c r="D2" t="n">
-        <v>16.89882323320035</v>
+        <v>6.887941892995622</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.076396394482004</v>
+        <v>0.5144357970253287</v>
       </c>
       <c r="C2" t="n">
-        <v>4.356014563743098</v>
+        <v>20.88079192162541</v>
       </c>
       <c r="D2" t="n">
-        <v>11.19388732382213</v>
+        <v>13.95848885898115</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.21294144083032</v>
+        <v>0.6037748381117884</v>
       </c>
       <c r="C3" t="n">
-        <v>27.35149104031614</v>
+        <v>28.59340188618835</v>
       </c>
       <c r="D3" t="n">
-        <v>79.11413874672922</v>
+        <v>38.72503819401544</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.25438013305371</v>
+        <v>2.935425635697963</v>
       </c>
       <c r="C4" t="n">
-        <v>96.10328276872026</v>
+        <v>55.60717171624359</v>
       </c>
       <c r="D4" t="n">
-        <v>170.0632460681537</v>
+        <v>103.7609148618454</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48326621686347</v>
+        <v>9.645671194224914</v>
       </c>
       <c r="C5" t="n">
-        <v>251.0328879759095</v>
+        <v>114.5699570856028</v>
       </c>
       <c r="D5" t="n">
-        <v>164.8599832356456</v>
+        <v>136.0211444233956</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.78494049950772</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>288.0408494351972</v>
+        <v>262.1590347081386</v>
       </c>
       <c r="D6" t="n">
-        <v>85.5750203883775</v>
+        <v>110.8933119331985</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>13.35471402086936</v>
       </c>
       <c r="C7" t="n">
-        <v>188.7625945909427</v>
+        <v>385.0110154267674</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>64.67753875577986</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>95.54859531582082</v>
+        <v>366.6729500591412</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>217.6593565177433</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>88.25911861178827</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.228207435741766</v>
+        <v>3.25645713498667</v>
       </c>
       <c r="C2" t="n">
-        <v>4.612250714551515</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="D2" t="n">
-        <v>19.94813160259094</v>
+        <v>9.596583809012571</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.30620747273377</v>
+        <v>4.545491870662732</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66855449105885</v>
+        <v>21.53954463117502</v>
       </c>
       <c r="D3" t="n">
-        <v>17.33275571847744</v>
+        <v>7.755806863549802</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39656465751588</v>
+        <v>11.67835320180492</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13495614817134</v>
+        <v>59.94887976926525</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576066430295985</v>
+        <v>0.778556880120328</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.237223091529233</v>
+        <v>1.904590546238812</v>
       </c>
       <c r="C2" t="n">
-        <v>7.267878254539137</v>
+        <v>6.032839642596649</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10619298297468</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.83835578616454</v>
+        <v>8.811185645615124</v>
       </c>
       <c r="C3" t="n">
-        <v>19.73803759388213</v>
+        <v>33.86047831947249</v>
       </c>
       <c r="D3" t="n">
-        <v>29.89912633283661</v>
+        <v>14.25006792714245</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.33253473429918</v>
+        <v>5.807037670619883</v>
       </c>
       <c r="C4" t="n">
-        <v>35.09748042682347</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="D4" t="n">
-        <v>24.15982925380975</v>
+        <v>18.25068982194821</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43688889004783</v>
+        <v>13.63081137079644</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12159064974054</v>
+        <v>73.76674388901604</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249871345273228</v>
+        <v>1.603624867152523</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.282784396552087</v>
+        <v>1.162389281828224</v>
       </c>
       <c r="C2" t="n">
-        <v>8.872054003278425</v>
+        <v>10.59600297193582</v>
       </c>
       <c r="D2" t="n">
-        <v>37.02268767485146</v>
+        <v>22.1766988912312</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05157496443535</v>
+        <v>7.564366061221674</v>
       </c>
       <c r="C3" t="n">
-        <v>25.10819753611218</v>
+        <v>27.22877257728529</v>
       </c>
       <c r="D3" t="n">
-        <v>39.04410619789565</v>
+        <v>23.699389580518</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.83174559414208</v>
+        <v>12.62233023350124</v>
       </c>
       <c r="C4" t="n">
-        <v>43.0614178036736</v>
+        <v>66.5448228892573</v>
       </c>
       <c r="D4" t="n">
-        <v>33.70634392990574</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.56637061435918</v>
+        <v>5.890486225480863</v>
       </c>
       <c r="C5" t="n">
-        <v>39.31899555508476</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D5" t="n">
-        <v>31.31775176547326</v>
+        <v>26.31083847381452</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>20.06201433628357</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72692220336727</v>
+        <v>14.84310305154013</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0342254405403</v>
+        <v>87.40938463684743</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181730550841817</v>
+        <v>2.473850508590022</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73398742987812</v>
+        <v>1.432369900496096</v>
       </c>
       <c r="C2" t="n">
-        <v>6.403940274801944</v>
+        <v>8.975137512224341</v>
       </c>
       <c r="D2" t="n">
-        <v>30.62365613857076</v>
+        <v>31.01930046338222</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10204500797944</v>
+        <v>5.546874528994479</v>
       </c>
       <c r="C3" t="n">
-        <v>30.36054775383261</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="D3" t="n">
-        <v>58.4974369575462</v>
+        <v>35.94178345247573</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.46086594611503</v>
+        <v>13.96241584979814</v>
       </c>
       <c r="C4" t="n">
-        <v>53.47579745032376</v>
+        <v>67.6041286621396</v>
       </c>
       <c r="D4" t="n">
-        <v>45.03963942773092</v>
+        <v>28.52467954689108</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.64815877344793</v>
+        <v>12.86089492563322</v>
       </c>
       <c r="C5" t="n">
-        <v>61.04016351154545</v>
+        <v>88.97088569736721</v>
       </c>
       <c r="D5" t="n">
-        <v>35.83379120500859</v>
+        <v>27.9798095710341</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.35096695650162</v>
+        <v>6.359761628110839</v>
       </c>
       <c r="C6" t="n">
-        <v>38.19882142453915</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04444781785013</v>
+        <v>16.08653974097931</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7185405259746</v>
+        <v>101.5991983640799</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014815939283376</v>
+        <v>3.386639945469329</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.182646130718912</v>
+        <v>2.599667920845554</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3250406055637</v>
+        <v>6.632687489891451</v>
       </c>
       <c r="D2" t="n">
-        <v>33.18798114206342</v>
+        <v>26.96370069713865</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.70167187109599</v>
+        <v>5.193445355465627</v>
       </c>
       <c r="C3" t="n">
-        <v>25.56961895710818</v>
+        <v>35.25946879802419</v>
       </c>
       <c r="D3" t="n">
-        <v>64.69226497134358</v>
+        <v>51.52211951887261</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.32199755145973</v>
+        <v>12.31602494977624</v>
       </c>
       <c r="C4" t="n">
-        <v>54.62444226429253</v>
+        <v>80.0094926530023</v>
       </c>
       <c r="D4" t="n">
-        <v>55.16047651081129</v>
+        <v>39.48785616021521</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.83759502263855</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C5" t="n">
-        <v>60.37748381117885</v>
+        <v>108.3849465488479</v>
       </c>
       <c r="D5" t="n">
-        <v>34.95021827118646</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.5585166327252</v>
+        <v>11.75348351524281</v>
       </c>
       <c r="C6" t="n">
-        <v>46.32965591111124</v>
+        <v>92.86057010159307</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>35.30070220160257</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>39.76470901281281</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.2611134982632</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049026770172306</v>
+        <v>17.35267931877864</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08462597036537</v>
+        <v>115.395317469878</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405641731357691</v>
+        <v>4.338169829694661</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.975497365122835</v>
+        <v>1.77598159698248</v>
       </c>
       <c r="C2" t="n">
-        <v>5.896376711706344</v>
+        <v>7.127488332831843</v>
       </c>
       <c r="D2" t="n">
-        <v>25.83567258495906</v>
+        <v>23.32632545290422</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78788574262046</v>
+        <v>7.048948516492098</v>
       </c>
       <c r="C3" t="n">
-        <v>34.93058331710152</v>
+        <v>30.0414797499524</v>
       </c>
       <c r="D3" t="n">
-        <v>76.93956758182253</v>
+        <v>59.97005851391641</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.43159344143688</v>
+        <v>11.14185469549705</v>
       </c>
       <c r="C4" t="n">
-        <v>60.53358169615408</v>
+        <v>83.39161349413257</v>
       </c>
       <c r="D4" t="n">
-        <v>76.27001564752621</v>
+        <v>54.61167954413732</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.10252803406495</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C5" t="n">
-        <v>84.25849671698251</v>
+        <v>128.3880560228766</v>
       </c>
       <c r="D5" t="n">
-        <v>47.19752088166541</v>
+        <v>37.47821860962199</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.61513920440203</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C6" t="n">
-        <v>75.59260973159593</v>
+        <v>131.8241729877405</v>
       </c>
       <c r="D6" t="n">
-        <v>36.38749691020379</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>49.1669067763845</v>
+        <v>84.61977987214533</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>26.70353755551324</v>
+        <v>38.80357801035517</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.34594471145593</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266749610064815</v>
+        <v>17.74852620280266</v>
       </c>
       <c r="C21" t="n">
-        <v>75.39252720442246</v>
+        <v>128.6768149703193</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450062207548611</v>
+        <v>5.324557860840798</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.228387362191013</v>
+        <v>1.648354395430395</v>
       </c>
       <c r="C2" t="n">
-        <v>4.665265090580843</v>
+        <v>4.447317100238051</v>
       </c>
       <c r="D2" t="n">
-        <v>26.78305911955723</v>
+        <v>18.33119313369644</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98914402199105</v>
+        <v>8.511752595819846</v>
       </c>
       <c r="C3" t="n">
-        <v>27.75891633757857</v>
+        <v>45.88688769649592</v>
       </c>
       <c r="D3" t="n">
-        <v>79.75718349301087</v>
+        <v>65.06532909895735</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.77542612210151</v>
+        <v>8.525497063679301</v>
       </c>
       <c r="C4" t="n">
-        <v>76.12962572581891</v>
+        <v>116.1152279720873</v>
       </c>
       <c r="D4" t="n">
-        <v>97.71138550827655</v>
+        <v>50.13196476965913</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.63115026730624</v>
+        <v>9.670214886831083</v>
       </c>
       <c r="C5" t="n">
-        <v>99.77011044408214</v>
+        <v>78.76070957320037</v>
       </c>
       <c r="D5" t="n">
-        <v>63.88723185386119</v>
+        <v>33.52668410002858</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.30949687321178</v>
+        <v>6.400013283984958</v>
       </c>
       <c r="C6" t="n">
-        <v>106.4253781311713</v>
+        <v>55.70829172978102</v>
       </c>
       <c r="D6" t="n">
-        <v>42.58625191481815</v>
+        <v>25.68055644768807</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>81.98476903394689</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>26.88908787161589</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>47.56567627075796</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.49991487010665</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.471158657997735</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.05053490247452</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537263825748019</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
